--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/58.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/58.xlsx
@@ -426,13 +426,13 @@
         <v>-6.888401947765533</v>
       </c>
       <c r="E2">
-        <v>-6.506042569631574</v>
+        <v>-8.688440991200133</v>
       </c>
       <c r="F2">
-        <v>-6.682237914192282</v>
+        <v>-7.338997193986711</v>
       </c>
       <c r="G2">
-        <v>-1.763042109243822</v>
+        <v>-4.22575362536212</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.139079503875532</v>
       </c>
       <c r="E3">
-        <v>-7.884152308119825</v>
+        <v>-9.654441481094352</v>
       </c>
       <c r="F3">
-        <v>-6.394285337235251</v>
+        <v>-6.777842676969052</v>
       </c>
       <c r="G3">
-        <v>-1.956990419662025</v>
+        <v>-4.001563481442674</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.415080778263438</v>
       </c>
       <c r="E4">
-        <v>-7.594194117408692</v>
+        <v>-10.32354162962368</v>
       </c>
       <c r="F4">
-        <v>-6.594897324808755</v>
+        <v>-7.38669049763017</v>
       </c>
       <c r="G4">
-        <v>-1.036496543013211</v>
+        <v>-4.054290540246646</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.832983929178723</v>
       </c>
       <c r="E5">
-        <v>-7.876585228053007</v>
+        <v>-9.75165423261701</v>
       </c>
       <c r="F5">
-        <v>-6.716814569517592</v>
+        <v>-7.449599651782693</v>
       </c>
       <c r="G5">
-        <v>-1.022658462659057</v>
+        <v>-4.006492883750649</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.379620164955131</v>
       </c>
       <c r="E6">
-        <v>-8.119234450806008</v>
+        <v>-11.31351133244049</v>
       </c>
       <c r="F6">
-        <v>-6.875990475519538</v>
+        <v>-7.670317181879178</v>
       </c>
       <c r="G6">
-        <v>-1.439416419506828</v>
+        <v>-3.260749463937804</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.058593228045678</v>
       </c>
       <c r="E7">
-        <v>-10.32165325596248</v>
+        <v>-11.1403560718092</v>
       </c>
       <c r="F7">
-        <v>-6.865460414887782</v>
+        <v>-7.006228907034575</v>
       </c>
       <c r="G7">
-        <v>-2.015722808074235</v>
+        <v>-4.754950950905697</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.846244272770634</v>
       </c>
       <c r="E8">
-        <v>-11.29496270290508</v>
+        <v>-12.51869223399784</v>
       </c>
       <c r="F8">
-        <v>-6.93149263710555</v>
+        <v>-7.492196193863788</v>
       </c>
       <c r="G8">
-        <v>-1.04990094190172</v>
+        <v>-4.358864040405135</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.720078731627658</v>
       </c>
       <c r="E9">
-        <v>-11.69234535402617</v>
+        <v>-14.00265052394137</v>
       </c>
       <c r="F9">
-        <v>-7.002819980051591</v>
+        <v>-7.681326709476835</v>
       </c>
       <c r="G9">
-        <v>-0.8938815517269472</v>
+        <v>-4.322984347850514</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.637303928542257</v>
       </c>
       <c r="E10">
-        <v>-12.59995117159147</v>
+        <v>-13.89937867419645</v>
       </c>
       <c r="F10">
-        <v>-6.822641758052045</v>
+        <v>-7.269883475983976</v>
       </c>
       <c r="G10">
-        <v>-1.046352037083621</v>
+        <v>-3.876772467339847</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.566245327808386</v>
       </c>
       <c r="E11">
-        <v>-12.60564799189312</v>
+        <v>-13.90911036483894</v>
       </c>
       <c r="F11">
-        <v>-6.63528182565246</v>
+        <v>-7.252858637393002</v>
       </c>
       <c r="G11">
-        <v>-0.6890878941220923</v>
+        <v>-4.317568295348266</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.474107151147633</v>
       </c>
       <c r="E12">
-        <v>-12.5197337830196</v>
+        <v>-15.51272905196116</v>
       </c>
       <c r="F12">
-        <v>-6.618055064557268</v>
+        <v>-7.018786903091051</v>
       </c>
       <c r="G12">
-        <v>-1.054588674385328</v>
+        <v>-3.604195389818415</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.332447854101412</v>
       </c>
       <c r="E13">
-        <v>-13.60805741280901</v>
+        <v>-15.51625220473912</v>
       </c>
       <c r="F13">
-        <v>-6.520216880513249</v>
+        <v>-6.880783957399094</v>
       </c>
       <c r="G13">
-        <v>-1.224303791456065</v>
+        <v>-4.242074614870726</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.128794454775321</v>
       </c>
       <c r="E14">
-        <v>-13.76791707375378</v>
+        <v>-17.62130429025667</v>
       </c>
       <c r="F14">
-        <v>-6.551853385806547</v>
+        <v>-7.302425465134426</v>
       </c>
       <c r="G14">
-        <v>0.03730869755925236</v>
+        <v>-3.629368778099033</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.859804859949139</v>
       </c>
       <c r="E15">
-        <v>-15.01431614572894</v>
+        <v>-16.3727089083878</v>
       </c>
       <c r="F15">
-        <v>-6.457887362725778</v>
+        <v>-6.640816877826921</v>
       </c>
       <c r="G15">
-        <v>-0.8260650263549769</v>
+        <v>-2.946922988997053</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.532145916159799</v>
       </c>
       <c r="E16">
-        <v>-16.02400735284916</v>
+        <v>-18.03091834967248</v>
       </c>
       <c r="F16">
-        <v>-6.379608738590394</v>
+        <v>-6.651050389526012</v>
       </c>
       <c r="G16">
-        <v>0.07635327164941674</v>
+        <v>-2.350955270471914</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.170025035028134</v>
       </c>
       <c r="E17">
-        <v>-16.14852680263807</v>
+        <v>-18.28657787824952</v>
       </c>
       <c r="F17">
-        <v>-6.055293086035437</v>
+        <v>-6.769648978489047</v>
       </c>
       <c r="G17">
-        <v>0.1683765060045379</v>
+        <v>-1.112069676583693</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.804322895453301</v>
       </c>
       <c r="E18">
-        <v>-16.47891068081568</v>
+        <v>-20.02074794253886</v>
       </c>
       <c r="F18">
-        <v>-5.863192725904463</v>
+        <v>-6.473797668278761</v>
       </c>
       <c r="G18">
-        <v>0.2192960069440681</v>
+        <v>-2.544519557607561</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.467911684851188</v>
       </c>
       <c r="E19">
-        <v>-18.87750297998443</v>
+        <v>-20.6453965902089</v>
       </c>
       <c r="F19">
-        <v>-5.31301962570446</v>
+        <v>-5.790788858862403</v>
       </c>
       <c r="G19">
-        <v>0.881802380263018</v>
+        <v>-1.245484661816322</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.197300791324118</v>
       </c>
       <c r="E20">
-        <v>-19.54961909220286</v>
+        <v>-20.6674185593082</v>
       </c>
       <c r="F20">
-        <v>-5.198086920009189</v>
+        <v>-5.698564120435659</v>
       </c>
       <c r="G20">
-        <v>0.2621245345856194</v>
+        <v>-1.245964690919516</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.020004102988324</v>
       </c>
       <c r="E21">
-        <v>-20.35552444050391</v>
+        <v>-22.34528610626018</v>
       </c>
       <c r="F21">
-        <v>-4.637836699069246</v>
+        <v>-5.508431514904618</v>
       </c>
       <c r="G21">
-        <v>0.8642333150861058</v>
+        <v>-1.582915326452077</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.9536247388492577</v>
       </c>
       <c r="E22">
-        <v>-20.36292396703245</v>
+        <v>-23.09625200790017</v>
       </c>
       <c r="F22">
-        <v>-4.390285251868033</v>
+        <v>-5.26254533447349</v>
       </c>
       <c r="G22">
-        <v>0.2238314543328696</v>
+        <v>-1.738378544976252</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.009251245967165</v>
       </c>
       <c r="E23">
-        <v>-21.54707010682416</v>
+        <v>-22.81976602736186</v>
       </c>
       <c r="F23">
-        <v>-4.138823634761599</v>
+        <v>-4.6740513022376</v>
       </c>
       <c r="G23">
-        <v>0.5095050500076589</v>
+        <v>-1.598683454855626</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.181348183345421</v>
       </c>
       <c r="E24">
-        <v>-21.65589839417649</v>
+        <v>-23.21855703389933</v>
       </c>
       <c r="F24">
-        <v>-4.073143391183537</v>
+        <v>-4.973669456967758</v>
       </c>
       <c r="G24">
-        <v>0.06988777621122011</v>
+        <v>-1.416679592743114</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.453121303742985</v>
       </c>
       <c r="E25">
-        <v>-21.77630598956644</v>
+        <v>-24.74245193611652</v>
       </c>
       <c r="F25">
-        <v>-3.653266527764484</v>
+        <v>-4.658590373238122</v>
       </c>
       <c r="G25">
-        <v>0.2595820356114591</v>
+        <v>-2.665235290151545</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.800575045059636</v>
       </c>
       <c r="E26">
-        <v>-21.66443003920694</v>
+        <v>-25.07798468924085</v>
       </c>
       <c r="F26">
-        <v>-4.004775598666973</v>
+        <v>-4.764069146471178</v>
       </c>
       <c r="G26">
-        <v>-1.667079325696968</v>
+        <v>-2.093318684969212</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.188689400971267</v>
       </c>
       <c r="E27">
-        <v>-21.08516122956777</v>
+        <v>-24.31552099209538</v>
       </c>
       <c r="F27">
-        <v>-3.999239754639555</v>
+        <v>-4.749334346633929</v>
       </c>
       <c r="G27">
-        <v>-1.169464604598038</v>
+        <v>-3.130025952228602</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.581118380521363</v>
       </c>
       <c r="E28">
-        <v>-21.83044842480215</v>
+        <v>-24.74871934414313</v>
       </c>
       <c r="F28">
-        <v>-4.231487059726919</v>
+        <v>-4.970201932865903</v>
       </c>
       <c r="G28">
-        <v>-0.708616802258253</v>
+        <v>-2.137398598824608</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.94458046560491</v>
       </c>
       <c r="E29">
-        <v>-21.50655837835154</v>
+        <v>-23.81113050017304</v>
       </c>
       <c r="F29">
-        <v>-3.688143691287249</v>
+        <v>-4.679467576468403</v>
       </c>
       <c r="G29">
-        <v>-1.09604994671916</v>
+        <v>-3.60230837886103</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.248438612173346</v>
       </c>
       <c r="E30">
-        <v>-21.70689353997687</v>
+        <v>-23.34224324447084</v>
       </c>
       <c r="F30">
-        <v>-3.722247214470323</v>
+        <v>-4.468363537205112</v>
       </c>
       <c r="G30">
-        <v>-1.042054948973647</v>
+        <v>-2.200510838985274</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.472744851822595</v>
       </c>
       <c r="E31">
-        <v>-21.45621080433426</v>
+        <v>-25.35410839185855</v>
       </c>
       <c r="F31">
-        <v>-4.159369051602595</v>
+        <v>-4.730051143407539</v>
       </c>
       <c r="G31">
-        <v>-1.379541892883569</v>
+        <v>-2.609945869100177</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.607079099453463</v>
       </c>
       <c r="E32">
-        <v>-20.76479886436914</v>
+        <v>-22.60057429996859</v>
       </c>
       <c r="F32">
-        <v>-3.994081624472969</v>
+        <v>-4.743109590533295</v>
       </c>
       <c r="G32">
-        <v>-1.969788988716847</v>
+        <v>-2.805943407207189</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.648999313845493</v>
       </c>
       <c r="E33">
-        <v>-20.38092917968694</v>
+        <v>-23.63167160372307</v>
       </c>
       <c r="F33">
-        <v>-3.848574684227181</v>
+        <v>-5.0124575822487</v>
       </c>
       <c r="G33">
-        <v>-1.225330060573239</v>
+        <v>-2.443147342649538</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.605626571016217</v>
       </c>
       <c r="E34">
-        <v>-21.59731805441327</v>
+        <v>-23.76717713145459</v>
       </c>
       <c r="F34">
-        <v>-3.665058010157888</v>
+        <v>-4.57995699897768</v>
       </c>
       <c r="G34">
-        <v>-0.08753528527220338</v>
+        <v>-2.691474674095809</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.488183439292701</v>
       </c>
       <c r="E35">
-        <v>-21.6394917328467</v>
+        <v>-22.29250221322678</v>
       </c>
       <c r="F35">
-        <v>-3.697511311777074</v>
+        <v>-4.990185134106918</v>
       </c>
       <c r="G35">
-        <v>-0.1481149580953268</v>
+        <v>-2.467003133805526</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.308424149561579</v>
       </c>
       <c r="E36">
-        <v>-19.26438409988173</v>
+        <v>-23.67586498156393</v>
       </c>
       <c r="F36">
-        <v>-3.899934267064882</v>
+        <v>-4.770618562284477</v>
       </c>
       <c r="G36">
-        <v>-0.8590049544707252</v>
+        <v>-1.631653177881228</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.083661880896416</v>
       </c>
       <c r="E37">
-        <v>-20.44278360615771</v>
+        <v>-22.95576515876022</v>
       </c>
       <c r="F37">
-        <v>-4.264462192445242</v>
+        <v>-4.961072660116352</v>
       </c>
       <c r="G37">
-        <v>0.1739084276006601</v>
+        <v>-1.396849424962879</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.835050665924056</v>
       </c>
       <c r="E38">
-        <v>-20.3476630096266</v>
+        <v>-21.10115127128886</v>
       </c>
       <c r="F38">
-        <v>-4.233271104440662</v>
+        <v>-4.988682197193166</v>
       </c>
       <c r="G38">
-        <v>-0.0006698808672666935</v>
+        <v>-2.497370768037261</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.584303155385888</v>
       </c>
       <c r="E39">
-        <v>-19.48290561312186</v>
+        <v>-22.09098059141144</v>
       </c>
       <c r="F39">
-        <v>-3.725836683927666</v>
+        <v>-4.694078055391289</v>
       </c>
       <c r="G39">
-        <v>-0.09775493935193352</v>
+        <v>-0.4094494229653943</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.353087407798609</v>
       </c>
       <c r="E40">
-        <v>-19.37655440105173</v>
+        <v>-21.04402004320809</v>
       </c>
       <c r="F40">
-        <v>-3.901996252166784</v>
+        <v>-4.516299147853634</v>
       </c>
       <c r="G40">
-        <v>0.1458085170633263</v>
+        <v>-0.70994764156504</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.146671489317013</v>
       </c>
       <c r="E41">
-        <v>-19.21651812962066</v>
+        <v>-22.018697089301</v>
       </c>
       <c r="F41">
-        <v>-3.999744164973623</v>
+        <v>-4.904801213381916</v>
       </c>
       <c r="G41">
-        <v>0.3647315830297906</v>
+        <v>-1.627895708694155</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.954253233106508</v>
       </c>
       <c r="E42">
-        <v>-18.52412803926988</v>
+        <v>-21.14773568340576</v>
       </c>
       <c r="F42">
-        <v>-4.119954570632096</v>
+        <v>-4.844249801411004</v>
       </c>
       <c r="G42">
-        <v>0.2420328337077826</v>
+        <v>-0.1572156477827833</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.765791311216622</v>
       </c>
       <c r="E43">
-        <v>-17.54950986333907</v>
+        <v>-20.18698822336044</v>
       </c>
       <c r="F43">
-        <v>-3.762346648249249</v>
+        <v>-4.787108108276033</v>
       </c>
       <c r="G43">
-        <v>0.7521912118550118</v>
+        <v>-1.055502384954166</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.573862741431214</v>
       </c>
       <c r="E44">
-        <v>-17.18031696291573</v>
+        <v>-20.69449430540006</v>
       </c>
       <c r="F44">
-        <v>-4.101241501535264</v>
+        <v>-4.904140808015177</v>
       </c>
       <c r="G44">
-        <v>0.4563476202835814</v>
+        <v>-1.500237762154318</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.374356434423926</v>
       </c>
       <c r="E45">
-        <v>-17.90018583354504</v>
+        <v>-19.77302682889728</v>
       </c>
       <c r="F45">
-        <v>-4.090294134394789</v>
+        <v>-4.888754313193726</v>
       </c>
       <c r="G45">
-        <v>1.292415964589902</v>
+        <v>-0.7431954504159405</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.16948917904217</v>
       </c>
       <c r="E46">
-        <v>-16.65390450189409</v>
+        <v>-18.8940726663785</v>
       </c>
       <c r="F46">
-        <v>-4.062688556582764</v>
+        <v>-4.869711041413524</v>
       </c>
       <c r="G46">
-        <v>0.3868824432330541</v>
+        <v>-0.7109441157723606</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.9623746853560805</v>
       </c>
       <c r="E47">
-        <v>-15.62171130742975</v>
+        <v>-19.14342855913686</v>
       </c>
       <c r="F47">
-        <v>-4.389201205168914</v>
+        <v>-5.348303009794536</v>
       </c>
       <c r="G47">
-        <v>0.06616010193400076</v>
+        <v>-0.3303075213035773</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.7574736577732148</v>
       </c>
       <c r="E48">
-        <v>-16.12115670573571</v>
+        <v>-19.34335162962749</v>
       </c>
       <c r="F48">
-        <v>-4.261860163626174</v>
+        <v>-4.673438408048325</v>
       </c>
       <c r="G48">
-        <v>0.8515572362162365</v>
+        <v>-1.893427945308018</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.5623722695801056</v>
       </c>
       <c r="E49">
-        <v>-15.29461057290771</v>
+        <v>-18.3487945826409</v>
       </c>
       <c r="F49">
-        <v>-4.158884437592471</v>
+        <v>-5.106472700212848</v>
       </c>
       <c r="G49">
-        <v>0.8622072612160718</v>
+        <v>-1.081162423429058</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.3839322868294763</v>
       </c>
       <c r="E50">
-        <v>-15.31242106117987</v>
+        <v>-16.86683334973474</v>
       </c>
       <c r="F50">
-        <v>-4.049497870013068</v>
+        <v>-4.373790162905773</v>
       </c>
       <c r="G50">
-        <v>0.2150452664716438</v>
+        <v>-1.033725616396841</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.2297190506453934</v>
       </c>
       <c r="E51">
-        <v>-15.21711479721444</v>
+        <v>-18.36841193204213</v>
       </c>
       <c r="F51">
-        <v>-4.069287067279442</v>
+        <v>-4.990458323377331</v>
       </c>
       <c r="G51">
-        <v>-0.231080539855002</v>
+        <v>-0.6584521057016767</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.1095925673542932</v>
       </c>
       <c r="E52">
-        <v>-14.77048499125994</v>
+        <v>-16.52028734782376</v>
       </c>
       <c r="F52">
-        <v>-4.507469195522101</v>
+        <v>-4.913118836849804</v>
       </c>
       <c r="G52">
-        <v>0.3258988838541396</v>
+        <v>-1.801000824397106</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.0317887744129634</v>
       </c>
       <c r="E53">
-        <v>-13.98064666873811</v>
+        <v>-16.78786581998899</v>
       </c>
       <c r="F53">
-        <v>-4.679081944077993</v>
+        <v>-4.923464395742412</v>
       </c>
       <c r="G53">
-        <v>-0.09293809559229395</v>
+        <v>-1.279573349234197</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.004930178914594687</v>
       </c>
       <c r="E54">
-        <v>-13.97772580300316</v>
+        <v>-16.11785091971011</v>
       </c>
       <c r="F54">
-        <v>-4.619384941448461</v>
+        <v>-4.905689672400477</v>
       </c>
       <c r="G54">
-        <v>-0.105829359922216</v>
+        <v>-1.085916366823451</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.03715371307288484</v>
       </c>
       <c r="E55">
-        <v>-14.62903357715635</v>
+        <v>-16.13852793202914</v>
       </c>
       <c r="F55">
-        <v>-4.744322709264521</v>
+        <v>-5.121943131447818</v>
       </c>
       <c r="G55">
-        <v>0.8856095076331799</v>
+        <v>-1.237572457977464</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.130863832061979</v>
       </c>
       <c r="E56">
-        <v>-13.37636709715457</v>
+        <v>-14.26257134655963</v>
       </c>
       <c r="F56">
-        <v>-4.451177952463722</v>
+        <v>-5.011990389003646</v>
       </c>
       <c r="G56">
-        <v>0.7034037022427723</v>
+        <v>-0.8786100051542891</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.2869601366133597</v>
       </c>
       <c r="E57">
-        <v>-14.16954290502006</v>
+        <v>-15.61284455532273</v>
       </c>
       <c r="F57">
-        <v>-4.569318454490716</v>
+        <v>-5.103334586941405</v>
       </c>
       <c r="G57">
-        <v>-0.01296855754565915</v>
+        <v>-0.5606155533795952</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.5034589526109248</v>
       </c>
       <c r="E58">
-        <v>-13.55422291380583</v>
+        <v>-14.55467150547639</v>
       </c>
       <c r="F58">
-        <v>-4.498742184075073</v>
+        <v>-5.201065078983173</v>
       </c>
       <c r="G58">
-        <v>0.3144642595614969</v>
+        <v>-2.351663727217318</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.7746437305360734</v>
       </c>
       <c r="E59">
-        <v>-12.78037010453107</v>
+        <v>-15.71821308853321</v>
       </c>
       <c r="F59">
-        <v>-4.561255807675214</v>
+        <v>-5.73745360289519</v>
       </c>
       <c r="G59">
-        <v>1.172944997168683</v>
+        <v>-1.268784281321713</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.09821814138944</v>
       </c>
       <c r="E60">
-        <v>-12.65185654066739</v>
+        <v>-14.17696960239264</v>
       </c>
       <c r="F60">
-        <v>-4.429691022455997</v>
+        <v>-5.198397326368616</v>
       </c>
       <c r="G60">
-        <v>0.02769156276766957</v>
+        <v>-2.133905973280677</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.470688495189934</v>
       </c>
       <c r="E61">
-        <v>-12.44884505090353</v>
+        <v>-14.39510166686811</v>
       </c>
       <c r="F61">
-        <v>-4.642402523223458</v>
+        <v>-5.697468195942175</v>
       </c>
       <c r="G61">
-        <v>0.360378215645649</v>
+        <v>-2.0375028871771</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.88414832251073</v>
       </c>
       <c r="E62">
-        <v>-12.50329089389775</v>
+        <v>-13.95487512316045</v>
       </c>
       <c r="F62">
-        <v>-4.534705769855829</v>
+        <v>-5.35800083296773</v>
       </c>
       <c r="G62">
-        <v>0.3069427000962727</v>
+        <v>-1.557453920709542</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.332255157674936</v>
       </c>
       <c r="E63">
-        <v>-12.88361025495794</v>
+        <v>-12.73194713196705</v>
       </c>
       <c r="F63">
-        <v>-4.650061325030522</v>
+        <v>-5.461792959400842</v>
       </c>
       <c r="G63">
-        <v>0.4855764268498067</v>
+        <v>-2.56909704769111</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.803945015922785</v>
       </c>
       <c r="E64">
-        <v>-11.42262944212932</v>
+        <v>-13.68856915219138</v>
       </c>
       <c r="F64">
-        <v>-4.852021046338066</v>
+        <v>-5.6383975490022</v>
       </c>
       <c r="G64">
-        <v>0.11662936868019</v>
+        <v>-2.260120521965391</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.283006794467496</v>
       </c>
       <c r="E65">
-        <v>-11.27688956314046</v>
+        <v>-13.53038955510346</v>
       </c>
       <c r="F65">
-        <v>-4.434043046311625</v>
+        <v>-5.180089685986135</v>
       </c>
       <c r="G65">
-        <v>-0.0009678299658011004</v>
+        <v>-2.286747239737749</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.756126747642496</v>
       </c>
       <c r="E66">
-        <v>-12.01627615674284</v>
+        <v>-14.92743284341778</v>
       </c>
       <c r="F66">
-        <v>-4.540415029680988</v>
+        <v>-5.37113054685968</v>
       </c>
       <c r="G66">
-        <v>0.08117342595459559</v>
+        <v>-2.654641544425878</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.206115181297471</v>
       </c>
       <c r="E67">
-        <v>-12.00919815186885</v>
+        <v>-13.05865388925043</v>
       </c>
       <c r="F67">
-        <v>-4.270635478103625</v>
+        <v>-5.77733686081666</v>
       </c>
       <c r="G67">
-        <v>-1.735465264901694</v>
+        <v>-3.295354596459806</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.613552940897826</v>
       </c>
       <c r="E68">
-        <v>-12.03381946504856</v>
+        <v>-14.39226684213931</v>
       </c>
       <c r="F68">
-        <v>-4.730868335659905</v>
+        <v>-5.085943120431007</v>
       </c>
       <c r="G68">
-        <v>-0.5314860631795481</v>
+        <v>-3.675199970544703</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.96490598011201</v>
       </c>
       <c r="E69">
-        <v>-12.16310286949354</v>
+        <v>-13.56619619908211</v>
       </c>
       <c r="F69">
-        <v>-4.396131502254877</v>
+        <v>-5.413848638369786</v>
       </c>
       <c r="G69">
-        <v>-0.5902780414114651</v>
+        <v>-3.098185125231892</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.246024038807375</v>
       </c>
       <c r="E70">
-        <v>-11.26829451947391</v>
+        <v>-13.95511513228286</v>
       </c>
       <c r="F70">
-        <v>-4.314515217902705</v>
+        <v>-5.411243442138889</v>
       </c>
       <c r="G70">
-        <v>-1.133720644410527</v>
+        <v>-2.977217791226923</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.446421747413814</v>
       </c>
       <c r="E71">
-        <v>-12.07964309353217</v>
+        <v>-13.55710755174871</v>
       </c>
       <c r="F71">
-        <v>-5.186388084411838</v>
+        <v>-5.222343751663018</v>
       </c>
       <c r="G71">
-        <v>-1.085485995903346</v>
+        <v>-4.420556056529453</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.565673481448844</v>
       </c>
       <c r="E72">
-        <v>-13.24485115502381</v>
+        <v>-14.30755720735183</v>
       </c>
       <c r="F72">
-        <v>-4.760408410247639</v>
+        <v>-5.3501559457156</v>
       </c>
       <c r="G72">
-        <v>-1.75928464005675</v>
+        <v>-3.514035992601903</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.605313466139574</v>
       </c>
       <c r="E73">
-        <v>-12.63685823475399</v>
+        <v>-12.92728738676192</v>
       </c>
       <c r="F73">
-        <v>-4.717427423555571</v>
+        <v>-5.401232837047396</v>
       </c>
       <c r="G73">
-        <v>-1.381531530752671</v>
+        <v>-5.122209630850286</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.571269783637039</v>
       </c>
       <c r="E74">
-        <v>-12.15395082352404</v>
+        <v>-14.23622921325701</v>
       </c>
       <c r="F74">
-        <v>-4.517538397732466</v>
+        <v>-5.324309073322671</v>
       </c>
       <c r="G74">
-        <v>-1.76527672748283</v>
+        <v>-3.700495849010274</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.476598661510677</v>
       </c>
       <c r="E75">
-        <v>-12.19422707134826</v>
+        <v>-15.39841225411153</v>
       </c>
       <c r="F75">
-        <v>-4.707350302815629</v>
+        <v>-5.322743580025259</v>
       </c>
       <c r="G75">
-        <v>-1.896831186122389</v>
+        <v>-4.295708763152459</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.332285135213507</v>
       </c>
       <c r="E76">
-        <v>-13.45666146978458</v>
+        <v>-15.38130367931055</v>
       </c>
       <c r="F76">
-        <v>-4.474996889431931</v>
+        <v>-5.45143473086091</v>
       </c>
       <c r="G76">
-        <v>-1.785716035642291</v>
+        <v>-3.095755184806067</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.150453208133299</v>
       </c>
       <c r="E77">
-        <v>-13.46963101934254</v>
+        <v>-15.54503971400588</v>
       </c>
       <c r="F77">
-        <v>-4.592550628417254</v>
+        <v>-5.241925483454469</v>
       </c>
       <c r="G77">
-        <v>-2.106915095498999</v>
+        <v>-4.808141486085167</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.945271775169805</v>
       </c>
       <c r="E78">
-        <v>-14.32186265674206</v>
+        <v>-15.07571772479894</v>
       </c>
       <c r="F78">
-        <v>-4.545516146434618</v>
+        <v>-5.909489200930504</v>
       </c>
       <c r="G78">
-        <v>-1.732777101923805</v>
+        <v>-4.530552242617278</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.72531967668422</v>
       </c>
       <c r="E79">
-        <v>-14.26672848569867</v>
+        <v>-17.19685042151773</v>
       </c>
       <c r="F79">
-        <v>-5.013996944398508</v>
+        <v>-5.705905389206679</v>
       </c>
       <c r="G79">
-        <v>-2.000888253512761</v>
+        <v>-4.381796189355667</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.49995232381304</v>
       </c>
       <c r="E80">
-        <v>-14.74509383749893</v>
+        <v>-15.3259566699888</v>
       </c>
       <c r="F80">
-        <v>-5.307870997773367</v>
+        <v>-5.527248316738913</v>
       </c>
       <c r="G80">
-        <v>-3.234175714894074</v>
+        <v>-4.715836855359208</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.279660921812019</v>
       </c>
       <c r="E81">
-        <v>-15.97524474473457</v>
+        <v>-18.43985313798714</v>
       </c>
       <c r="F81">
-        <v>-5.034662722889077</v>
+        <v>-5.770483373467595</v>
       </c>
       <c r="G81">
-        <v>-1.978644698034398</v>
+        <v>-4.48625383275629</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.068870864692897</v>
       </c>
       <c r="E82">
-        <v>-16.28712074964282</v>
+        <v>-18.52831234925297</v>
       </c>
       <c r="F82">
-        <v>-5.224611618533927</v>
+        <v>-6.039942224597082</v>
       </c>
       <c r="G82">
-        <v>-1.674319488791355</v>
+        <v>-5.255475641533647</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.874332759305601</v>
       </c>
       <c r="E83">
-        <v>-16.48161870827227</v>
+        <v>-19.1767535993593</v>
       </c>
       <c r="F83">
-        <v>-5.130564034598513</v>
+        <v>-6.014872951808634</v>
       </c>
       <c r="G83">
-        <v>-3.126318141224619</v>
+        <v>-4.787354570644084</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.701707303680398</v>
       </c>
       <c r="E84">
-        <v>-17.89429428886107</v>
+        <v>-18.77799429213988</v>
       </c>
       <c r="F84">
-        <v>-5.090158945577906</v>
+        <v>-5.859987305131614</v>
       </c>
       <c r="G84">
-        <v>-2.170444464397613</v>
+        <v>-5.187745190345698</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.549629227499483</v>
       </c>
       <c r="E85">
-        <v>-18.22134521016903</v>
+        <v>-20.46199792137226</v>
       </c>
       <c r="F85">
-        <v>-5.195323353186748</v>
+        <v>-5.988158208574044</v>
       </c>
       <c r="G85">
-        <v>-2.536613974859781</v>
+        <v>-4.345519231336333</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.421267058792353</v>
       </c>
       <c r="E86">
-        <v>-20.13356128701795</v>
+        <v>-21.83137223349971</v>
       </c>
       <c r="F86">
-        <v>-5.138456433028106</v>
+        <v>-5.922716312736255</v>
       </c>
       <c r="G86">
-        <v>-2.024025656286727</v>
+        <v>-4.979346348648576</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.317530539051461</v>
       </c>
       <c r="E87">
-        <v>-21.0168673130581</v>
+        <v>-23.43081113911285</v>
       </c>
       <c r="F87">
-        <v>-5.280517229201897</v>
+        <v>-6.253778156564505</v>
       </c>
       <c r="G87">
-        <v>-2.616278942716803</v>
+        <v>-4.450039775102203</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.233690408996618</v>
       </c>
       <c r="E88">
-        <v>-22.89585344763874</v>
+        <v>-24.69655585204878</v>
       </c>
       <c r="F88">
-        <v>-5.405439159958803</v>
+        <v>-5.815123292106088</v>
       </c>
       <c r="G88">
-        <v>-2.579713967235553</v>
+        <v>-5.309785141105391</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.171519314407664</v>
       </c>
       <c r="E89">
-        <v>-25.05233994093541</v>
+        <v>-26.44805185789147</v>
       </c>
       <c r="F89">
-        <v>-5.3748047445835</v>
+        <v>-5.966995146426026</v>
       </c>
       <c r="G89">
-        <v>-2.224406356687734</v>
+        <v>-4.929009503723958</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.129053217487249</v>
       </c>
       <c r="E90">
-        <v>-25.69649272615648</v>
+        <v>-26.76903009555515</v>
       </c>
       <c r="F90">
-        <v>-5.444831469046486</v>
+        <v>-6.01972542673354</v>
       </c>
       <c r="G90">
-        <v>-2.383196673478876</v>
+        <v>-4.454320310484481</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.099752359696916</v>
       </c>
       <c r="E91">
-        <v>-27.32763547829732</v>
+        <v>-29.31098029638472</v>
       </c>
       <c r="F91">
-        <v>-5.079636011622769</v>
+        <v>-5.664392497898223</v>
       </c>
       <c r="G91">
-        <v>-2.850854267992942</v>
+        <v>-4.812107519641214</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.084389946253448</v>
       </c>
       <c r="E92">
-        <v>-29.33667032943023</v>
+        <v>-30.1620118881722</v>
       </c>
       <c r="F92">
-        <v>-5.140603146396484</v>
+        <v>-6.035035903671051</v>
       </c>
       <c r="G92">
-        <v>-3.431871562862731</v>
+        <v>-5.287011898340745</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.080318743984825</v>
       </c>
       <c r="E93">
-        <v>-31.35118010563842</v>
+        <v>-33.82786820330645</v>
       </c>
       <c r="F93">
-        <v>-5.518452414084562</v>
+        <v>-5.795795745114064</v>
       </c>
       <c r="G93">
-        <v>-3.576333838559908</v>
+        <v>-5.111364283663633</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.082730899093171</v>
       </c>
       <c r="E94">
-        <v>-33.30527551011028</v>
+        <v>-34.42353235309039</v>
       </c>
       <c r="F94">
-        <v>-5.282505571978731</v>
+        <v>-5.486532029505922</v>
       </c>
       <c r="G94">
-        <v>-3.892120156459908</v>
+        <v>-4.810889238882762</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.093515373568435</v>
       </c>
       <c r="E95">
-        <v>-34.93716546046239</v>
+        <v>-37.21021034624248</v>
       </c>
       <c r="F95">
-        <v>-5.010759057654392</v>
+        <v>-5.589177552856257</v>
       </c>
       <c r="G95">
-        <v>-3.907034164114325</v>
+        <v>-5.627643860512975</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.11567421414672</v>
       </c>
       <c r="E96">
-        <v>-38.07887128734183</v>
+        <v>-38.51119337966909</v>
       </c>
       <c r="F96">
-        <v>-4.707243402666337</v>
+        <v>-5.471759220726703</v>
       </c>
       <c r="G96">
-        <v>-4.757500070970936</v>
+        <v>-6.00413896251213</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.147777973552416</v>
       </c>
       <c r="E97">
-        <v>-40.57827647486933</v>
+        <v>-41.43298518755105</v>
       </c>
       <c r="F97">
-        <v>-4.977551912019457</v>
+        <v>-5.337191729091813</v>
       </c>
       <c r="G97">
-        <v>-4.041131121728044</v>
+        <v>-6.581216708190187</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.206684656245404</v>
       </c>
       <c r="E98">
-        <v>-42.61726265308899</v>
+        <v>-44.05375574272112</v>
       </c>
       <c r="F98">
-        <v>-4.662454615671794</v>
+        <v>-5.397941104302155</v>
       </c>
       <c r="G98">
-        <v>-4.248785090678829</v>
+        <v>-7.342374028033879</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.28801248097575</v>
       </c>
       <c r="E99">
-        <v>-43.54675684977037</v>
+        <v>-45.47342102294076</v>
       </c>
       <c r="F99">
-        <v>-5.068466133801175</v>
+        <v>-5.073431051846077</v>
       </c>
       <c r="G99">
-        <v>-4.992807026811253</v>
+        <v>-7.431311833946399</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.414684783527871</v>
       </c>
       <c r="E100">
-        <v>-47.75580588636168</v>
+        <v>-47.56765005557998</v>
       </c>
       <c r="F100">
-        <v>-4.827013538080319</v>
+        <v>-4.817274538553324</v>
       </c>
       <c r="G100">
-        <v>-5.811872409227877</v>
+        <v>-7.15104435913724</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.568277257550086</v>
       </c>
       <c r="E101">
-        <v>-49.44264547244136</v>
+        <v>-50.8075230098792</v>
       </c>
       <c r="F101">
-        <v>-4.866154037927447</v>
+        <v>-4.76913146242988</v>
       </c>
       <c r="G101">
-        <v>-6.213527657325493</v>
+        <v>-8.149531378145744</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.798314997894446</v>
       </c>
       <c r="E102">
-        <v>-51.7579885696901</v>
+        <v>-52.47764120568555</v>
       </c>
       <c r="F102">
-        <v>-4.356361479306361</v>
+        <v>-4.09169650598291</v>
       </c>
       <c r="G102">
-        <v>-6.499151594817193</v>
+        <v>-7.784888029177179</v>
       </c>
     </row>
   </sheetData>
